--- a/data/business_trips.xlsx
+++ b/data/business_trips.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>市场推广活动</t>
+          <t>市场推广活动（跨月，5月7天，6月2天）</t>
         </is>
       </c>
     </row>
@@ -535,6 +535,36 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>产品评审会议</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>跨月出差（5月2天，6月2天）</t>
         </is>
       </c>
     </row>
